--- a/docs/pin_list.xlsx
+++ b/docs/pin_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b2da16fa1785921/MyDocuments/Community/ISHIKAI/shuttle/OpenSUSI-TR10/2026/RISE-A/OpenSUSI-TR1um-v2609_04/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{80FD4C0D-4061-4E0A-82DD-26CB8133CE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{489E4457-5A9A-4EB4-BC5A-2134C10E1031}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{80FD4C0D-4061-4E0A-82DD-26CB8133CE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{187B9E4B-985B-42F2-8CA2-EE63E8F9C079}"/>
   <bookViews>
     <workbookView xWindow="38330" yWindow="0" windowWidth="19200" windowHeight="9980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Pin Number</t>
     <phoneticPr fontId="1"/>
@@ -78,10 +78,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>none</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>555timer</t>
   </si>
   <si>
@@ -114,6 +110,14 @@
   </si>
   <si>
     <t>RST</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ClkDiv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TICK</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -247,6 +251,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -571,10 +579,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -582,10 +590,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18.350000000000001" thickBot="1">
@@ -593,10 +601,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18.350000000000001" thickTop="1">
@@ -604,10 +612,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -626,10 +634,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18.350000000000001" thickBot="1">
@@ -637,10 +645,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18.350000000000001" thickTop="1">
@@ -648,19 +656,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -668,18 +678,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:3" ht="18.350000000000001" thickBot="1">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="16" spans="1:3" ht="18.350000000000001" thickTop="1">
       <c r="A16" s="3">
